--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6771-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6771-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F66DBA5F-F459-4B10-9006-547E366CA868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB26DA34-DF08-4531-9B4C-D3F80E5BD22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7A7709C4-6955-4B10-915A-44B88C24E9F9}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{493FD48E-B8E0-43EB-89C6-8B885B5D8841}"/>
   </bookViews>
   <sheets>
     <sheet name="6771-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1451,19 +1451,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2911B54-BAFE-4612-8CDE-8EF5659787BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6C9620-901A-4C58-9DDD-FB694CE4DFA8}">
   <dimension ref="A1:X13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1653,7 +1653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2023</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2022</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2021</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2020</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2019</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>39</v>
       </c>
